--- a/Key.xlsx
+++ b/Key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beabo\OneDrive\Documents\NAU\Dark Web\Datasets\NanoDrop Readings\Dark_Web_Samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A986DEC9-FFDF-4253-B132-38F906B2D452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85802B28-7997-425D-A452-748E0D2C554C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="3975" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>Tube</t>
   </si>
@@ -463,6 +463,15 @@
   </si>
   <si>
     <t>4.14B.S</t>
+  </si>
+  <si>
+    <t>4.7A.S</t>
+  </si>
+  <si>
+    <t>4.8B.S</t>
+  </si>
+  <si>
+    <t>4.11A.S</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1175,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="C28">
         <v>8.6200000000000003E-4</v>
@@ -1180,7 +1189,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="C29">
         <v>5.1599999999999997E-4</v>
@@ -2720,7 +2729,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="C139">
         <v>1.7639999999999999E-3</v>
